--- a/PPG/Editais.xlsx
+++ b/PPG/Editais.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B60E1BFE-DBA8-C242-9CCA-C5B6601EFC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C515732B-2D3D-7646-8E01-4F3FA301B174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="680" windowWidth="27640" windowHeight="16900" activeTab="2" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
+    <workbookView xWindow="1060" yWindow="680" windowWidth="27640" windowHeight="16900" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sede" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="208">
   <si>
     <t>Publicação</t>
   </si>
@@ -584,33 +584,9 @@
     <t>2024 PPGCR Edital N° 07</t>
   </si>
   <si>
-    <t>2019-1 UNISUAM IC.pdf</t>
-  </si>
-  <si>
-    <t>2023-1 UNISUAM IC Alunos.pdf</t>
-  </si>
-  <si>
-    <t>2023-1 UNISUAM IC Projetos.pdf</t>
-  </si>
-  <si>
-    <t>2024-1 UNISUAM IC Projetos.pdf</t>
-  </si>
-  <si>
-    <t>2024-1 UNISUAM IC Aunos.pdf</t>
-  </si>
-  <si>
-    <t>2025-1 UNISUAM IC Projetos.pdf</t>
-  </si>
-  <si>
-    <t>2022-1 UNISUAM IC.pdf</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1aFt9JTMAceutp62X8BVKxp0gsh4Qymp9</t>
   </si>
   <si>
-    <t>2025-1 UNISUAM IC Aunos.pdf</t>
-  </si>
-  <si>
     <t>https://drive.google.com/file/d/1hZJIPvb_8PUldtAilKARNggfaYc_aiBH</t>
   </si>
   <si>
@@ -654,6 +630,39 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1mc2CxHGC69cTTu0OhheL128mWT44LTNv</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jziUwu75S-I8LHa9TbDRmhsV2B6fbM26</t>
+  </si>
+  <si>
+    <t>2025 UNISUAM IC Projetos.pdf</t>
+  </si>
+  <si>
+    <t>2026 UNISUAM IC Projetos.pdf</t>
+  </si>
+  <si>
+    <t>2024 UNISUAM IC Projetos.pdf</t>
+  </si>
+  <si>
+    <t>2025 UNISUAM IC Aunos.pdf</t>
+  </si>
+  <si>
+    <t>2024 UNISUAM IC Aunos.pdf</t>
+  </si>
+  <si>
+    <t>2023 UNISUAM IC Projetos.pdf</t>
+  </si>
+  <si>
+    <t>2023 UNISUAM IC Alunos.pdf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EjHmuNl50QJOfBtD9qDqwtU__vceErXJ</t>
+  </si>
+  <si>
+    <t>2026-2</t>
+  </si>
+  <si>
+    <t>2026-1 PPGCR Edital N° 5.pdf</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109E75EB-4039-C840-A144-16CD29903E29}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
@@ -1445,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>109</v>
@@ -1588,7 +1597,7 @@
         <v>20</v>
       </c>
       <c r="B50" t="s">
-        <v>187</v>
+        <v>65</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>126</v>
@@ -1643,7 +1652,7 @@
         <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>146</v>
@@ -1654,7 +1663,7 @@
         <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>135</v>
@@ -1698,7 +1707,7 @@
         <v>155</v>
       </c>
       <c r="B60" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>163</v>
@@ -1709,7 +1718,7 @@
         <v>155</v>
       </c>
       <c r="B61" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>162</v>
@@ -1742,10 +1751,10 @@
         <v>168</v>
       </c>
       <c r="B64" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1753,10 +1762,10 @@
         <v>168</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1783,46 +1792,68 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B69" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B71" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>203</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B73" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1901,6 +1932,8 @@
     <hyperlink ref="C69" r:id="rId68" xr:uid="{58E0BEE0-CEAE-9E4F-8272-2FBDFDB4BDD7}"/>
     <hyperlink ref="C70" r:id="rId69" xr:uid="{DC3BB191-A02F-DA46-BF70-86BF90F77374}"/>
     <hyperlink ref="C71" r:id="rId70" xr:uid="{1613F4D7-EBC8-0F44-8E5C-4ECB9A8FE0E7}"/>
+    <hyperlink ref="C72" r:id="rId71" xr:uid="{5D1CAD7F-C422-5140-959C-31633A8FD51F}"/>
+    <hyperlink ref="C73" r:id="rId72" xr:uid="{851FFC45-6AFE-8C4E-B2A3-5E0512776E28}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2039,24 +2072,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>
